--- a/data/exports/payments_2026-07_20260801_210618.xlsx
+++ b/data/exports/payments_2026-07_20260801_210618.xlsx
@@ -8,22 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Programming\OSBB_cl\data\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A713DF05-F5E7-4659-A289-74D0A89D4C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD1D795-26C3-4B75-8353-8DDD161668E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9703" yWindow="3249" windowWidth="16380" windowHeight="12754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8074" yWindow="2846" windowWidth="17100" windowHeight="11083" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Платежи" sheetId="1" r:id="rId1"/>
-    <sheet name="Сводка по авто" sheetId="2" r:id="rId2"/>
-    <sheet name="Ведомость" sheetId="3" r:id="rId3"/>
-    <sheet name="Неполные данные" sheetId="4" r:id="rId4"/>
+    <sheet name="Платежи (2)" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
+    <sheet name="Сводка по авто" sheetId="2" r:id="rId4"/>
+    <sheet name="Ведомость" sheetId="3" r:id="rId5"/>
+    <sheet name="Неполные данные" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="160">
   <si>
     <t>Дата платежа</t>
   </si>
@@ -1873,6 +1875,1021 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201D6A9A-4E2E-4930-B985-0F947C32C47E}">
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="14.53515625" customWidth="1"/>
+    <col min="2" max="2" width="11" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.15234375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2">
+        <v>500</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2">
+        <v>400</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>500</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2">
+        <v>500</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2">
+        <v>500</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2">
+        <v>500</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2">
+        <v>500</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2">
+        <v>300</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2">
+        <v>500</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2">
+        <v>200</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2">
+        <v>200</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2">
+        <v>700</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2">
+        <v>600</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="2">
+        <v>300</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="2">
+        <v>500</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="2">
+        <v>500</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2">
+        <v>700</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="2">
+        <v>200</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="2">
+        <v>500</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="2">
+        <v>200</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="2">
+        <v>200</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="2">
+        <v>200</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="2">
+        <v>200</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="2">
+        <v>200</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="2">
+        <v>200</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="2">
+        <v>500</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="2">
+        <v>500</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="2">
+        <v>500</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="2">
+        <v>500</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="2">
+        <v>200</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="2">
+        <v>600</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="2">
+        <v>500</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="2">
+        <v>100</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="2">
+        <v>500</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A41" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="2">
+        <v>500</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="2">
+        <v>500</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="2">
+        <v>500</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D44" s="2">
+        <v>500</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" s="2">
+        <v>500</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="2">
+        <v>500</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="2">
+        <v>700</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="2">
+        <v>500</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" s="2">
+        <v>200</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A51" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" s="5">
+        <v>25100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A52" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B52" s="6">
+        <v>20600</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A53" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" s="6">
+        <v>4500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36323C71-E6A8-4057-992C-414BF74A4CC6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -1979,7 +2996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -2319,7 +3336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
